--- a/publication/web-root/matchsync-donor/StructureDefinition-nmdp-abo-rh-observation.xlsx
+++ b/publication/web-root/matchsync-donor/StructureDefinition-nmdp-abo-rh-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:51:12+00:00</t>
+    <t>2026-09-03T16:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
